--- a/AWS-Batch02Credentials.xlsx
+++ b/AWS-Batch02Credentials.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mahesh\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/622d7d18e0d997fa/Desktop/2026-04sep-02sep-batch02-learning-devops/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E1F88D-F6B0-48B5-8B40-C183115C87BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{48E1F88D-F6B0-48B5-8B40-C183115C87BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03BBFD23-3892-4879-BBF5-5C5E3BBA59AB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{5EE13838-65F7-425C-93A5-71EBBF2FBF97}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{5EE13838-65F7-425C-93A5-71EBBF2FBF97}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="52">
   <si>
     <t>Username</t>
   </si>
@@ -110,6 +110,72 @@
   </si>
   <si>
     <t>awsuserb225</t>
+  </si>
+  <si>
+    <t>Bharath</t>
+  </si>
+  <si>
+    <t>Assigned To</t>
+  </si>
+  <si>
+    <t>Kushal</t>
+  </si>
+  <si>
+    <t>Kalyan</t>
+  </si>
+  <si>
+    <t>Sreesailam</t>
+  </si>
+  <si>
+    <t>Prathyusha</t>
+  </si>
+  <si>
+    <t>Pritha</t>
+  </si>
+  <si>
+    <t>Vara Prasad</t>
+  </si>
+  <si>
+    <t>Sreedhar</t>
+  </si>
+  <si>
+    <t>Lahari</t>
+  </si>
+  <si>
+    <t>Naveen</t>
+  </si>
+  <si>
+    <t>Sarfarz</t>
+  </si>
+  <si>
+    <t>Hari Prasad</t>
+  </si>
+  <si>
+    <t>Sudeep</t>
+  </si>
+  <si>
+    <t>Rajesh</t>
+  </si>
+  <si>
+    <t>Charan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harsha </t>
+  </si>
+  <si>
+    <t>Divakar</t>
+  </si>
+  <si>
+    <t>Prem</t>
+  </si>
+  <si>
+    <t>Vishnu</t>
+  </si>
+  <si>
+    <t>Tejaswi</t>
+  </si>
+  <si>
+    <t>Sri Laxmi</t>
   </si>
 </sst>
 </file>
@@ -460,7 +526,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -590,6 +656,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -635,10 +712,14 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1016,15 +1097,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75505C2D-0233-41D3-97D6-43C37FA659A3}">
-  <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:D26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="55.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1034,8 +1115,11 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D1" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -1045,8 +1129,11 @@
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D2" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
@@ -1056,8 +1143,11 @@
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D3" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1067,8 +1157,11 @@
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D4" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
@@ -1078,8 +1171,11 @@
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D5" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>9</v>
       </c>
@@ -1089,8 +1185,11 @@
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D6" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -1100,8 +1199,11 @@
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D7" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -1111,8 +1213,11 @@
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D8" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
@@ -1122,8 +1227,11 @@
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D9" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
@@ -1133,8 +1241,11 @@
       <c r="C10" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D10" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>14</v>
       </c>
@@ -1144,8 +1255,11 @@
       <c r="C11" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D11" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
@@ -1155,8 +1269,11 @@
       <c r="C12" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D12" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
@@ -1166,8 +1283,11 @@
       <c r="C13" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D13" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>17</v>
       </c>
@@ -1177,8 +1297,11 @@
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D14" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
@@ -1188,8 +1311,11 @@
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D15" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>19</v>
       </c>
@@ -1199,8 +1325,11 @@
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
@@ -1210,8 +1339,11 @@
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>21</v>
       </c>
@@ -1221,8 +1353,11 @@
       <c r="C18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
@@ -1232,8 +1367,11 @@
       <c r="C19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -1243,8 +1381,11 @@
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>24</v>
       </c>
@@ -1254,8 +1395,11 @@
       <c r="C21" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>25</v>
       </c>
@@ -1265,8 +1409,11 @@
       <c r="C22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>26</v>
       </c>
@@ -1276,8 +1423,11 @@
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D23" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>27</v>
       </c>
@@ -1288,7 +1438,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>28</v>
       </c>
@@ -1299,7 +1449,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>29</v>
       </c>
